--- a/pensum/ok07/OK07_Produktvalg_knapp_faktor_Regneark_Knapp_faktor.xlsx
+++ b/pensum/ok07/OK07_Produktvalg_knapp_faktor_Regneark_Knapp_faktor.xlsx
@@ -1013,7 +1013,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1168,6 +1168,14 @@
     </xf>
     <xf numFmtId="170" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1570,7 +1578,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="32.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
         <v>21</v>
       </c>
@@ -1932,8 +1940,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row ht="27" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A38" t="s">
         <v>88</v>
       </c>
       <c r="B38" s="21" t="s">
@@ -1943,8 +1951,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+    <row ht="27" customHeight="true" r="39" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A39" t="s">
         <v>90</v>
       </c>
       <c r="B39" s="21" t="s">
@@ -2262,8 +2270,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row ht="27" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A15" t="s">
         <v>124</v>
       </c>
       <c r="B15" s="26" t="n">
@@ -2283,8 +2291,8 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+    <row ht="27" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A17" t="s">
         <v>127</v>
       </c>
       <c r="B17" s="26" t="n">
@@ -2310,8 +2318,8 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row ht="27" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="27" t="n">
@@ -2327,8 +2335,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row ht="27" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A23" t="s">
         <v>132</v>
       </c>
       <c r="B23" s="31" t="str">
@@ -2336,8 +2344,8 @@
         <v>OK — rangering per montørtime og rangering per oppdrag gir ulik rekkefølge. Det er derfor måltallet betyr noe</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row ht="27" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A24" t="s">
         <v>133</v>
       </c>
       <c r="B24" s="31" t="str">
@@ -2345,8 +2353,8 @@
         <v>OK — alle fire oppdragstypene gir positivt dekningsbidrag</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row ht="27" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A25" t="s">
         <v>134</v>
       </c>
       <c r="B25" s="31" t="str">
@@ -2883,8 +2891,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="19" t="s">
+    <row ht="27" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B29" t="s">
         <v>163</v>
       </c>
       <c r="C29" s="30" t="n">
@@ -2892,8 +2900,8 @@
         <v>424800</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="19" t="s">
+    <row ht="27" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B30" t="s">
         <v>164</v>
       </c>
       <c r="C30" s="30" t="n">
@@ -2927,8 +2935,8 @@
         <v>1344000</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="21" t="s">
+    <row ht="27" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="B34" t="s">
         <v>168</v>
       </c>
       <c r="C34" s="34" t="n">
@@ -2944,8 +2952,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="19" t="s">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B37" t="s">
         <v>171</v>
       </c>
       <c r="C37" s="20" t="str">
@@ -2956,8 +2964,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="19" t="s">
+    <row ht="27" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B38" t="s">
         <v>173</v>
       </c>
       <c r="C38" s="33" t="n">
@@ -2965,8 +2973,8 @@
         <v>300</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="19" t="s">
+    <row ht="39.75" customHeight="true" r="39" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B39" t="s">
         <v>174</v>
       </c>
       <c r="C39" s="30" t="n">
@@ -2974,8 +2982,8 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="21" t="s">
+    <row ht="52.5" customHeight="true" r="40" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="B40" t="s">
         <v>175</v>
       </c>
       <c r="C40" s="29" t="n">
@@ -2991,8 +2999,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19" t="s">
+    <row ht="27" customHeight="true" r="43" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B43" t="s">
         <v>177</v>
       </c>
       <c r="C43" s="31" t="str">
@@ -3000,8 +3008,8 @@
         <v>OK — begge planene holder seg innenfor de montørtimene dere har</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="19" t="s">
+    <row ht="27" customHeight="true" r="44" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B44" t="s">
         <v>178</v>
       </c>
       <c r="C44" s="31" t="str">
@@ -3009,8 +3017,8 @@
         <v>OK — rangering per montørtime gir minst like mye dekningsbidrag som rangering per oppdrag</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="19" t="s">
+    <row ht="27" customHeight="true" r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B45" t="s">
         <v>179</v>
       </c>
       <c r="C45" s="31" t="str">
@@ -3551,8 +3559,8 @@
         <v>49800</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19" t="s">
+    <row ht="27" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B33" t="s">
         <v>199</v>
       </c>
       <c r="C33" s="26" t="n">
@@ -3568,8 +3576,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="19" t="s">
+    <row ht="27" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B36" t="s">
         <v>201</v>
       </c>
       <c r="C36" s="31" t="str">
@@ -3577,8 +3585,8 @@
         <v>OK — begge planene holder seg innenfor det grossisten kan levere</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="19" t="s">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B37" t="s">
         <v>202</v>
       </c>
       <c r="C37" s="31" t="str">
@@ -3586,8 +3594,8 @@
         <v>OK — når materiellet er knapt, er det dekningsbidrag per materiellkrone som skal styre</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="19" t="s">
+    <row ht="27" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="B38" t="s">
         <v>203</v>
       </c>
       <c r="C38" s="31" t="str">
@@ -3683,7 +3691,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22"/>
       <c r="B9" s="22" t="s">
         <v>212</v>
@@ -3946,8 +3954,8 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row ht="27" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A36" t="s">
         <v>240</v>
       </c>
       <c r="B36" s="29" t="n">
@@ -3990,8 +3998,8 @@
         <v>OK — begge avtalene holder seg innenfor de timene som er satt av</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="s">
+    <row ht="27" customHeight="true" r="42" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A42" t="s">
         <v>245</v>
       </c>
       <c r="B42" s="31" t="str">
@@ -4310,8 +4318,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row ht="27" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A20" t="s">
         <v>133</v>
       </c>
       <c r="B20" s="31" t="str">
